--- a/games.xlsx
+++ b/games.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -602,42 +602,62 @@
           <t>updates_en</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>plan_items_ja</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>plan_items_en</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>history_items_ja</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>history_items_en</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>links_text_ja</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>links_text_en</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="V1" s="10" t="inlineStr">
         <is>
           <t>steam_url</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="W1" s="10" t="inlineStr">
         <is>
           <t>x_url</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="X1" s="7" t="inlineStr">
         <is>
           <t>meta_platform</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="Y1" s="7" t="inlineStr">
         <is>
           <t>meta_status_ja</t>
         </is>
       </c>
-      <c r="V1" s="7" t="inlineStr">
+      <c r="Z1" s="7" t="inlineStr">
         <is>
           <t>meta_status_en</t>
         </is>
       </c>
-      <c r="W1" s="8" t="inlineStr">
+      <c r="AA1" s="8" t="inlineStr">
         <is>
           <t>meta_links</t>
         </is>
@@ -681,80 +701,100 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>極限の状況でAIと会話し、優秀さと人間らしさを示すADV</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>In development</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Steamページ準備中。公開情報、ストアリンク、関連リンクをこのページにまとめます。</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Steam page in preparation. Release information store links and related links are collected here.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>極限の状況でAIと会話し、優秀さと人間らしさを示すADVです。公開予定や関連リンクをこのページにまとめます。</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>A tense ADV where you talk with an AI in an extreme situation and prove both competence and humanity. Release plans and related links are collected here.</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>リリース時期、ストアリンク、イベント展示などの情報をここに追加できます。</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Release timing store links event appearances and other notes can be added here.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>リリース予定: 未定</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Release date: TBA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Steamページ準備中</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Steam page in preparation</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>ストアページ、更新情報、問い合わせ先などを必要に応じて追加できます。</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Store pages updates contact links and other references can be added here.</t>
+        </is>
+      </c>
+      <c r="V2" s="11" t="inlineStr">
+        <is>
+          <t>https://store.steampowered.com/app/4733690/Sak_Winik__The_Appointed_One/</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BogosorGames</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
           <t>開発中</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>In development</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Steamページ準備中。公開情報、ストアリンク、関連リンクをこのページにまとめます。</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Steam page in preparation. Release information store links and related links are collected here.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>AIに自分が人間であることを証明する会話ゲームです。詳細な訴求文やルール説明は、Steamページ公開後に差し替えます。</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>A conversation game about proving to an AI that you are human. Detailed copy and rule explanations can be replaced after the Steam page is published.</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>リリース時期、ストアリンク、イベント展示などの情報をここに追加できます。</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Release timing store links event appearances and other notes can be added here.</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>ストアページ、更新情報、問い合わせ先などを必要に応じて追加できます。</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Store pages updates contact links and other references can be added here.</t>
-        </is>
-      </c>
-      <c r="R2" s="11" t="inlineStr">
-        <is>
-          <t>https://store.steampowered.com/app/4733690/Sak_Winik__The_Appointed_One/</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/BogosorGames</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>Steam</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>開発中</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>Steam / X</t>
         </is>
@@ -818,12 +858,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Reversiと2048を組み合わせたパズルゲームです。詳細な訴求文やルール説明は、Steamページ公開後に差し替えます。</t>
+          <t>Reversiと2048を組み合わせたパズルゲームです。駒をひっくり返すたびにスコアが倍になり、盤面の判断がそのまま得点につながります。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>A puzzle game that combines Reversi and 2048. Detailed copy and rule explanations can be replaced after the Steam page is published.</t>
+          <t>A puzzle game that combines Reversi and 2048. Your score doubles every time you flip a piece, turning board control into score growth.</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -836,42 +876,62 @@
           <t>Release timing store links event appearances and other notes can be added here.</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026年10月リリース予定</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Planned release in October 2026</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Steamページ準備中</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Steam page in preparation</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>ストアページ、更新情報、問い合わせ先などを必要に応じて追加できます。</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>Store pages updates contact links and other references can be added here.</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>https://store.steampowered.com/app/4619930/Reversi2048/</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>https://x.com/BogosorGames</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>Steam / Android / iOS</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>開発中</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>In development</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>Steam / X</t>
         </is>
@@ -915,80 +975,100 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>コマンド入力でスキルを発動！ド派手に決めるエアホッケー！</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>In development</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Skill Hockeyの公開情報、ストアリンク、関連リンクをこのページにまとめます。</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Release information store links and related links for Skill Hockey are collected here.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>コマンド入力でスキルを発動し、派手な一撃を狙うエアホッケーです。公開情報やストアリンクをこのページにまとめます。</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>An air hockey game where command inputs trigger special skills and set up flashy shots. Release information and store links are collected here.</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>リリース時期、ストアリンク、イベント展示などの情報をここに追加できます。</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Release timing store links event appearances and other notes can be added here.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>リリース予定: 未定</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Release date: TBA</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Steamページ準備中</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Steam page in preparation</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>ストアページ、更新情報、問い合わせ先などを必要に応じて追加できます。</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Store pages updates contact links and other references can be added here.</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>https://store.steampowered.com/app/3074910/Skill_Hockey/</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/BogosorGames</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
           <t>開発中</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>In development</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Skill Hockeyの公開情報、ストアリンク、関連リンクをこのページにまとめます。</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Release information store links and related links for Skill Hockey are collected here.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Skill Hockeyの概要やルール説明は、Steamページ公開後に差し替えます。</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Details and rule explanations for Skill Hockey can be replaced after the Steam page is published.</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>リリース時期、ストアリンク、イベント展示などの情報をここに追加できます。</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Release timing store links event appearances and other notes can be added here.</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>ストアページ、更新情報、問い合わせ先などを必要に応じて追加できます。</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Store pages updates contact links and other references can be added here.</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>https://store.steampowered.com/app/3074910/Skill_Hockey/</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>https://x.com/BogosorGames</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>Steam</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>開発中</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>Steam / X</t>
         </is>
@@ -1032,7 +1112,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026年8月gamescom/2026年9月TGS出展</t>
+          <t>速度と戦術で競い合う マルチスレッドタイピングバトル</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1052,12 +1132,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>NyctoTypeの概要やルール説明は、Steamページ公開後に差し替えます。</t>
+          <t>速度と戦術で競い合う、マルチスレッドなタイピングバトルです。今後の展示情報や公開予定をこのページにまとめます。</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Details and rule explanations for NyctoType can be replaced after the Steam page is published.</t>
+          <t>A multithreaded typing battle driven by speed and tactics. Exhibition news and release plans are collected on this page.</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1070,42 +1150,62 @@
           <t>Release timing store links event appearances and other notes can be added here.</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026年8月 gamescom出展|2026年9月 TGS出展</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Exhibiting at gamescom in August 2026|Exhibiting at TGS in September 2026</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Steamページ準備中</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Steam page in preparation</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>ストアページ、更新情報、問い合わせ先などを必要に応じて追加できます。</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>Store pages updates contact links and other references can be added here.</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>https://store.steampowered.com/app/3968600/NyctoType/</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>https://x.com/BogosorGames</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>Steam</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>開発中</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>In development</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>Steam / X</t>
         </is>
@@ -1149,80 +1249,100 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
+          <t>現代の生き方を表現したレトロな1ボタンジャンプゲーム</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Available now</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Happy Runnerの公開情報、ストアリンク、関連リンクをこのページにまとめます。</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Release information store links and related links for Happy Runner are collected here.</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>現代の生き方を表現した、レトロな1ボタンジャンプゲームです。公開中のストア情報と関連リンクをまとめます。</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>A retro one-button jumping game about modern life. Store information and related links are collected here.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>リリース時期、ストアリンク、イベント展示などの情報をここに追加できます。</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>Release timing store links event appearances and other notes can be added here.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>追加情報があれば掲載予定</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Future updates will be posted here when available</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Steamで発売中</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Available now on Steam</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>ストアページ、更新情報、問い合わせ先などを必要に応じて追加できます。</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>Store pages updates contact links and other references can be added here.</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>https://store.steampowered.com/app/2988640/HAPPY_RUNNER/</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>https://x.com/BogosorGames</t>
+        </is>
+      </c>
+      <c r="X6" s="5" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
           <t>発売中</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="Z6" s="5" t="inlineStr">
         <is>
           <t>Available now</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Happy Runnerの公開情報、ストアリンク、関連リンクをこのページにまとめます。</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>Release information store links and related links for Happy Runner are collected here.</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>Happy Runnerの概要やルール説明は、Steamページ公開後に差し替えます。</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>Details and rule explanations for Happy Runner can be replaced after the Steam page is published.</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>リリース時期、ストアリンク、イベント展示などの情報をここに追加できます。</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>Release timing store links event appearances and other notes can be added here.</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>ストアページ、更新情報、問い合わせ先などを必要に応じて追加できます。</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>Store pages updates contact links and other references can be added here.</t>
-        </is>
-      </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>https://store.steampowered.com/app/2988640/HAPPY_RUNNER/</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr">
-        <is>
-          <t>https://x.com/BogosorGames</t>
-        </is>
-      </c>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>Steam</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="inlineStr">
-        <is>
-          <t>発売中</t>
-        </is>
-      </c>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>Available now</t>
-        </is>
-      </c>
-      <c r="W6" s="6" t="inlineStr">
+      <c r="AA6" s="6" t="inlineStr">
         <is>
           <t>Steam / X</t>
         </is>
